--- a/docentes/Jiménez Nieto Enrique - Estadisticos 20231.xlsx
+++ b/docentes/Jiménez Nieto Enrique - Estadisticos 20231.xlsx
@@ -746,10 +746,10 @@
         <v>18</v>
       </c>
       <c r="C9">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E9">
         <v>4</v>
@@ -758,7 +758,7 @@
         <v>8</v>
       </c>
       <c r="G9">
-        <v>57.14</v>
+        <v>66.67</v>
       </c>
       <c r="H9">
         <v>7.3</v>
@@ -969,10 +969,10 @@
         <v>18</v>
       </c>
       <c r="C9">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D9">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E9">
         <v>12</v>
@@ -1207,10 +1207,10 @@
         <v>18</v>
       </c>
       <c r="C9">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E9">
         <v>4</v>
@@ -1219,7 +1219,7 @@
         <v>8</v>
       </c>
       <c r="G9">
-        <v>57.14</v>
+        <v>66.67</v>
       </c>
       <c r="H9">
         <v>7.3</v>

--- a/docentes/Jiménez Nieto Enrique - Estadisticos 20231.xlsx
+++ b/docentes/Jiménez Nieto Enrique - Estadisticos 20231.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="64">
   <si>
     <t>Mat</t>
   </si>
@@ -100,79 +100,115 @@
     <t>GARCIA</t>
   </si>
   <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
     <t>SANCHEZ</t>
   </si>
   <si>
+    <t>TENTZOHUA</t>
+  </si>
+  <si>
+    <t>ALVAREZ</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>SALAZAR</t>
+  </si>
+  <si>
+    <t>VENTURA</t>
+  </si>
+  <si>
+    <t>MORENO</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
     <t>DE LOS SANTOS</t>
   </si>
   <si>
-    <t>TENTZOHUA</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
     <t>LOPEZ</t>
   </si>
   <si>
     <t>GONZALEZ</t>
   </si>
   <si>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
     <t>CRUZ</t>
   </si>
   <si>
+    <t>LEON</t>
+  </si>
+  <si>
+    <t>RIVERA</t>
+  </si>
+  <si>
+    <t>NAJERA</t>
+  </si>
+  <si>
+    <t>GOMEZ</t>
+  </si>
+  <si>
+    <t>ROSALES</t>
+  </si>
+  <si>
+    <t>AGUILAR</t>
+  </si>
+  <si>
+    <t>LAGUNES</t>
+  </si>
+  <si>
+    <t>BRETON</t>
+  </si>
+  <si>
     <t>QUIÑONES</t>
   </si>
   <si>
-    <t>LEÓN</t>
-  </si>
-  <si>
-    <t>VERA</t>
-  </si>
-  <si>
-    <t>TZOPITL</t>
-  </si>
-  <si>
-    <t>LAGUNES</t>
-  </si>
-  <si>
-    <t>BRETON</t>
-  </si>
-  <si>
     <t>ABIGAIL</t>
   </si>
   <si>
     <t>MIROSLAVA</t>
   </si>
   <si>
+    <t>MARIA FERNANDA</t>
+  </si>
+  <si>
     <t>ANGEL DAVID</t>
   </si>
   <si>
+    <t>RUBI</t>
+  </si>
+  <si>
+    <t>PEDRO ANGEL</t>
+  </si>
+  <si>
+    <t>ALBERTO SHAKIB</t>
+  </si>
+  <si>
+    <t>RONALDO</t>
+  </si>
+  <si>
+    <t>LUIS GUILLERMO</t>
+  </si>
+  <si>
+    <t>GUSTAVO</t>
+  </si>
+  <si>
+    <t>NAHOMY</t>
+  </si>
+  <si>
+    <t>VANESSA AMAIRANY</t>
+  </si>
+  <si>
     <t>GABRIELA</t>
-  </si>
-  <si>
-    <t>RUBI</t>
-  </si>
-  <si>
-    <t>MARIA JOSE</t>
-  </si>
-  <si>
-    <t>JOSE MANUEL</t>
-  </si>
-  <si>
-    <t>MARIA FERNANDA</t>
-  </si>
-  <si>
-    <t>VANESSA AMAIRANY</t>
   </si>
 </sst>
 </file>
@@ -694,10 +730,10 @@
         <v>16</v>
       </c>
       <c r="C7">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E7">
         <v>2</v>
@@ -706,7 +742,7 @@
         <v>33</v>
       </c>
       <c r="G7">
-        <v>94.29000000000001</v>
+        <v>91.67</v>
       </c>
       <c r="H7">
         <v>8.6</v>
@@ -923,10 +959,10 @@
         <v>16</v>
       </c>
       <c r="C7">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D7">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E7">
         <v>35</v>
@@ -1155,10 +1191,10 @@
         <v>16</v>
       </c>
       <c r="C7">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E7">
         <v>2</v>
@@ -1167,7 +1203,7 @@
         <v>33</v>
       </c>
       <c r="G7">
-        <v>94.29000000000001</v>
+        <v>91.67</v>
       </c>
       <c r="H7">
         <v>8.6</v>
@@ -1232,7 +1268,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1270,10 +1306,10 @@
         <v>25</v>
       </c>
       <c r="C2" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="D2" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="E2" t="s">
         <v>10</v>
@@ -1293,10 +1329,10 @@
         <v>26</v>
       </c>
       <c r="C3" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="D3" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
@@ -1310,16 +1346,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920102</v>
+        <v>21330051920080</v>
       </c>
       <c r="B4" t="s">
         <v>27</v>
       </c>
       <c r="C4" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D4" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="E4" t="s">
         <v>10</v>
@@ -1333,16 +1369,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920104</v>
+        <v>21330051920102</v>
       </c>
       <c r="B5" t="s">
         <v>28</v>
       </c>
       <c r="C5" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="D5" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
@@ -1362,10 +1398,10 @@
         <v>29</v>
       </c>
       <c r="C6" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="D6" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="E6" t="s">
         <v>10</v>
@@ -1379,22 +1415,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920109</v>
+        <v>21330051920135</v>
       </c>
       <c r="B7" t="s">
         <v>30</v>
       </c>
       <c r="C7" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="D7" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="E7" t="s">
         <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G7">
         <v>2</v>
@@ -1402,22 +1438,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>19330061430023</v>
+        <v>21330051920141</v>
       </c>
       <c r="B8" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D8" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="E8" t="s">
         <v>10</v>
       </c>
       <c r="F8" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G8">
         <v>2</v>
@@ -1425,47 +1461,162 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051920077</v>
+        <v>21330051920147</v>
       </c>
       <c r="B9" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C9" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="D9" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="E9" t="s">
         <v>10</v>
       </c>
       <c r="F9" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
+        <v>21330051920382</v>
+      </c>
+      <c r="B10" t="s">
+        <v>32</v>
+      </c>
+      <c r="C10" t="s">
+        <v>27</v>
+      </c>
+      <c r="D10" t="s">
+        <v>59</v>
+      </c>
+      <c r="E10" t="s">
+        <v>10</v>
+      </c>
+      <c r="F10" t="s">
+        <v>18</v>
+      </c>
+      <c r="G10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>21330051920213</v>
+      </c>
+      <c r="B11" t="s">
+        <v>33</v>
+      </c>
+      <c r="C11" t="s">
+        <v>46</v>
+      </c>
+      <c r="D11" t="s">
+        <v>60</v>
+      </c>
+      <c r="E11" t="s">
+        <v>10</v>
+      </c>
+      <c r="F11" t="s">
+        <v>15</v>
+      </c>
+      <c r="G11">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>19330051920208</v>
+      </c>
+      <c r="B12" t="s">
+        <v>34</v>
+      </c>
+      <c r="C12" t="s">
+        <v>47</v>
+      </c>
+      <c r="D12" t="s">
+        <v>61</v>
+      </c>
+      <c r="E12" t="s">
+        <v>10</v>
+      </c>
+      <c r="F12" t="s">
+        <v>16</v>
+      </c>
+      <c r="G12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>21330051920077</v>
+      </c>
+      <c r="B13" t="s">
+        <v>35</v>
+      </c>
+      <c r="C13" t="s">
+        <v>48</v>
+      </c>
+      <c r="D13" t="s">
+        <v>53</v>
+      </c>
+      <c r="E13" t="s">
+        <v>10</v>
+      </c>
+      <c r="F13" t="s">
+        <v>17</v>
+      </c>
+      <c r="G13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
         <v>21330051920082</v>
       </c>
-      <c r="B10" t="s">
-        <v>33</v>
-      </c>
-      <c r="C10" t="s">
-        <v>42</v>
-      </c>
-      <c r="D10" t="s">
-        <v>51</v>
-      </c>
-      <c r="E10" t="s">
-        <v>10</v>
-      </c>
-      <c r="F10" t="s">
+      <c r="B14" t="s">
+        <v>36</v>
+      </c>
+      <c r="C14" t="s">
+        <v>49</v>
+      </c>
+      <c r="D14" t="s">
+        <v>62</v>
+      </c>
+      <c r="E14" t="s">
+        <v>10</v>
+      </c>
+      <c r="F14" t="s">
         <v>17</v>
       </c>
-      <c r="G10">
+      <c r="G14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
+        <v>21330051920104</v>
+      </c>
+      <c r="B15" t="s">
+        <v>37</v>
+      </c>
+      <c r="C15" t="s">
+        <v>50</v>
+      </c>
+      <c r="D15" t="s">
+        <v>63</v>
+      </c>
+      <c r="E15" t="s">
+        <v>10</v>
+      </c>
+      <c r="F15" t="s">
+        <v>17</v>
+      </c>
+      <c r="G15">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Jiménez Nieto Enrique - Estadisticos 20231.xlsx
+++ b/docentes/Jiménez Nieto Enrique - Estadisticos 20231.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="40">
   <si>
     <t>Mat</t>
   </si>
@@ -94,121 +94,49 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
+    <t>TENTZOHUA</t>
+  </si>
+  <si>
+    <t>NUBE</t>
+  </si>
+  <si>
+    <t>VENTURA</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>LEON</t>
+  </si>
+  <si>
+    <t>ALEMAN</t>
+  </si>
+  <si>
+    <t>ROSALES</t>
   </si>
   <si>
     <t>SANCHEZ</t>
   </si>
   <si>
-    <t>TENTZOHUA</t>
-  </si>
-  <si>
-    <t>ALVAREZ</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>SALAZAR</t>
-  </si>
-  <si>
-    <t>VENTURA</t>
-  </si>
-  <si>
-    <t>MORENO</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>DE LOS SANTOS</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>LEON</t>
-  </si>
-  <si>
-    <t>RIVERA</t>
-  </si>
-  <si>
-    <t>NAJERA</t>
-  </si>
-  <si>
-    <t>GOMEZ</t>
-  </si>
-  <si>
-    <t>ROSALES</t>
-  </si>
-  <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>LAGUNES</t>
-  </si>
-  <si>
     <t>BRETON</t>
   </si>
   <si>
-    <t>QUIÑONES</t>
-  </si>
-  <si>
-    <t>ABIGAIL</t>
-  </si>
-  <si>
-    <t>MIROSLAVA</t>
-  </si>
-  <si>
-    <t>MARIA FERNANDA</t>
-  </si>
-  <si>
-    <t>ANGEL DAVID</t>
-  </si>
-  <si>
     <t>RUBI</t>
   </si>
   <si>
-    <t>PEDRO ANGEL</t>
-  </si>
-  <si>
-    <t>ALBERTO SHAKIB</t>
-  </si>
-  <si>
-    <t>RONALDO</t>
-  </si>
-  <si>
-    <t>LUIS GUILLERMO</t>
+    <t>CHRISTIAN YAIR</t>
   </si>
   <si>
     <t>GUSTAVO</t>
   </si>
   <si>
-    <t>NAHOMY</t>
+    <t>JOSE RAFAEL</t>
   </si>
   <si>
     <t>VANESSA AMAIRANY</t>
-  </si>
-  <si>
-    <t>GABRIELA</t>
   </si>
 </sst>
 </file>
@@ -733,16 +661,16 @@
         <v>36</v>
       </c>
       <c r="D7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E7">
         <v>2</v>
       </c>
       <c r="F7">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G7">
-        <v>91.67</v>
+        <v>94.44</v>
       </c>
       <c r="H7">
         <v>8.6</v>
@@ -850,16 +778,19 @@
         <v>27</v>
       </c>
       <c r="D2">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>96.3</v>
+      </c>
+      <c r="H2">
+        <v>8.6</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -873,16 +804,19 @@
         <v>24</v>
       </c>
       <c r="D3">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>75</v>
+      </c>
+      <c r="H3">
+        <v>7.5</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -916,16 +850,19 @@
         <v>30</v>
       </c>
       <c r="D5">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>96.67</v>
+      </c>
+      <c r="H5">
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -939,16 +876,19 @@
         <v>27</v>
       </c>
       <c r="D6">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>27</v>
+        <v>6</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>77.78</v>
+      </c>
+      <c r="H6">
+        <v>8.1</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -962,16 +902,19 @@
         <v>36</v>
       </c>
       <c r="D7">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>91.67</v>
+      </c>
+      <c r="H7">
+        <v>8.6</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -985,16 +928,19 @@
         <v>33</v>
       </c>
       <c r="D8">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="E8">
-        <v>33</v>
+        <v>5</v>
       </c>
       <c r="F8">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>84.84999999999999</v>
+      </c>
+      <c r="H8">
+        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -1008,16 +954,19 @@
         <v>12</v>
       </c>
       <c r="D9">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="E9">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="F9">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G9">
-        <v>0</v>
+        <v>75</v>
+      </c>
+      <c r="H9">
+        <v>7.3</v>
       </c>
     </row>
   </sheetData>
@@ -1073,16 +1022,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G2">
-        <v>92.59</v>
+        <v>96.3</v>
       </c>
       <c r="H2">
-        <v>8.6</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1099,16 +1048,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F3">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G3">
-        <v>83.33</v>
+        <v>75</v>
       </c>
       <c r="H3">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1154,7 +1103,7 @@
         <v>96.67</v>
       </c>
       <c r="H5">
-        <v>8.699999999999999</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1171,16 +1120,16 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F6">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G6">
-        <v>81.48</v>
+        <v>77.78</v>
       </c>
       <c r="H6">
-        <v>8.1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1194,10 +1143,10 @@
         <v>36</v>
       </c>
       <c r="D7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F7">
         <v>33</v>
@@ -1206,7 +1155,7 @@
         <v>91.67</v>
       </c>
       <c r="H7">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1223,16 +1172,16 @@
         <v>0</v>
       </c>
       <c r="E8">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F8">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="G8">
-        <v>72.73</v>
+        <v>84.84999999999999</v>
       </c>
       <c r="H8">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -1249,16 +1198,16 @@
         <v>0</v>
       </c>
       <c r="E9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F9">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G9">
-        <v>66.67</v>
+        <v>75</v>
       </c>
       <c r="H9">
-        <v>7.3</v>
+        <v>7.9</v>
       </c>
     </row>
   </sheetData>
@@ -1268,7 +1217,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1300,16 +1249,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920071</v>
+        <v>21330051920107</v>
       </c>
       <c r="B2" t="s">
         <v>25</v>
       </c>
       <c r="C2" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="D2" t="s">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="E2" t="s">
         <v>10</v>
@@ -1323,22 +1272,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920078</v>
+        <v>20330051920100</v>
       </c>
       <c r="B3" t="s">
         <v>26</v>
       </c>
       <c r="C3" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="D3" t="s">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -1346,22 +1295,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920080</v>
+        <v>21330051920213</v>
       </c>
       <c r="B4" t="s">
         <v>27</v>
       </c>
       <c r="C4" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="D4" t="s">
-        <v>53</v>
+        <v>37</v>
       </c>
       <c r="E4" t="s">
         <v>10</v>
       </c>
       <c r="F4" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -1369,22 +1318,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920102</v>
+        <v>20330051920235</v>
       </c>
       <c r="B5" t="s">
         <v>28</v>
       </c>
       <c r="C5" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="D5" t="s">
-        <v>54</v>
+        <v>38</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -1392,16 +1341,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920107</v>
+        <v>21330051920082</v>
       </c>
       <c r="B6" t="s">
         <v>29</v>
       </c>
       <c r="C6" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="D6" t="s">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="E6" t="s">
         <v>10</v>
@@ -1410,213 +1359,6 @@
         <v>17</v>
       </c>
       <c r="G6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>21330051920135</v>
-      </c>
-      <c r="B7" t="s">
-        <v>30</v>
-      </c>
-      <c r="C7" t="s">
-        <v>43</v>
-      </c>
-      <c r="D7" t="s">
-        <v>56</v>
-      </c>
-      <c r="E7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F7" t="s">
-        <v>18</v>
-      </c>
-      <c r="G7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>21330051920141</v>
-      </c>
-      <c r="B8" t="s">
-        <v>27</v>
-      </c>
-      <c r="C8" t="s">
-        <v>44</v>
-      </c>
-      <c r="D8" t="s">
-        <v>57</v>
-      </c>
-      <c r="E8" t="s">
-        <v>10</v>
-      </c>
-      <c r="F8" t="s">
-        <v>18</v>
-      </c>
-      <c r="G8">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>21330051920147</v>
-      </c>
-      <c r="B9" t="s">
-        <v>31</v>
-      </c>
-      <c r="C9" t="s">
-        <v>45</v>
-      </c>
-      <c r="D9" t="s">
-        <v>58</v>
-      </c>
-      <c r="E9" t="s">
-        <v>10</v>
-      </c>
-      <c r="F9" t="s">
-        <v>18</v>
-      </c>
-      <c r="G9">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>21330051920382</v>
-      </c>
-      <c r="B10" t="s">
-        <v>32</v>
-      </c>
-      <c r="C10" t="s">
-        <v>27</v>
-      </c>
-      <c r="D10" t="s">
-        <v>59</v>
-      </c>
-      <c r="E10" t="s">
-        <v>10</v>
-      </c>
-      <c r="F10" t="s">
-        <v>18</v>
-      </c>
-      <c r="G10">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>21330051920213</v>
-      </c>
-      <c r="B11" t="s">
-        <v>33</v>
-      </c>
-      <c r="C11" t="s">
-        <v>46</v>
-      </c>
-      <c r="D11" t="s">
-        <v>60</v>
-      </c>
-      <c r="E11" t="s">
-        <v>10</v>
-      </c>
-      <c r="F11" t="s">
-        <v>15</v>
-      </c>
-      <c r="G11">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>19330051920208</v>
-      </c>
-      <c r="B12" t="s">
-        <v>34</v>
-      </c>
-      <c r="C12" t="s">
-        <v>47</v>
-      </c>
-      <c r="D12" t="s">
-        <v>61</v>
-      </c>
-      <c r="E12" t="s">
-        <v>10</v>
-      </c>
-      <c r="F12" t="s">
-        <v>16</v>
-      </c>
-      <c r="G12">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>21330051920077</v>
-      </c>
-      <c r="B13" t="s">
-        <v>35</v>
-      </c>
-      <c r="C13" t="s">
-        <v>48</v>
-      </c>
-      <c r="D13" t="s">
-        <v>53</v>
-      </c>
-      <c r="E13" t="s">
-        <v>10</v>
-      </c>
-      <c r="F13" t="s">
-        <v>17</v>
-      </c>
-      <c r="G13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>21330051920082</v>
-      </c>
-      <c r="B14" t="s">
-        <v>36</v>
-      </c>
-      <c r="C14" t="s">
-        <v>49</v>
-      </c>
-      <c r="D14" t="s">
-        <v>62</v>
-      </c>
-      <c r="E14" t="s">
-        <v>10</v>
-      </c>
-      <c r="F14" t="s">
-        <v>17</v>
-      </c>
-      <c r="G14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>21330051920104</v>
-      </c>
-      <c r="B15" t="s">
-        <v>37</v>
-      </c>
-      <c r="C15" t="s">
-        <v>50</v>
-      </c>
-      <c r="D15" t="s">
-        <v>63</v>
-      </c>
-      <c r="E15" t="s">
-        <v>10</v>
-      </c>
-      <c r="F15" t="s">
-        <v>17</v>
-      </c>
-      <c r="G15">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Jiménez Nieto Enrique - Estadisticos 20231.xlsx
+++ b/docentes/Jiménez Nieto Enrique - Estadisticos 20231.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="48">
   <si>
     <t>Mat</t>
   </si>
@@ -97,6 +97,9 @@
     <t>TENTZOHUA</t>
   </si>
   <si>
+    <t>LORENZO</t>
+  </si>
+  <si>
     <t>NUBE</t>
   </si>
   <si>
@@ -106,6 +109,12 @@
     <t>LOPEZ</t>
   </si>
   <si>
+    <t>OFICIAL</t>
+  </si>
+  <si>
+    <t>TRUJILLO</t>
+  </si>
+  <si>
     <t>DE JESUS</t>
   </si>
   <si>
@@ -121,12 +130,21 @@
     <t>SANCHEZ</t>
   </si>
   <si>
+    <t>VILLASEÑOR</t>
+  </si>
+  <si>
+    <t>OSORIO</t>
+  </si>
+  <si>
     <t>BRETON</t>
   </si>
   <si>
     <t>RUBI</t>
   </si>
   <si>
+    <t>GREGORIO</t>
+  </si>
+  <si>
     <t>CHRISTIAN YAIR</t>
   </si>
   <si>
@@ -134,6 +152,12 @@
   </si>
   <si>
     <t>JOSE RAFAEL</t>
+  </si>
+  <si>
+    <t>MONICA AIME</t>
+  </si>
+  <si>
+    <t>KARINA YOSELIN</t>
   </si>
   <si>
     <t>VANESSA AMAIRANY</t>
@@ -710,7 +734,7 @@
         <v>18</v>
       </c>
       <c r="C9">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D9">
         <v>0</v>
@@ -719,13 +743,13 @@
         <v>4</v>
       </c>
       <c r="F9">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G9">
-        <v>66.67</v>
+        <v>69.23</v>
       </c>
       <c r="H9">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
     </row>
   </sheetData>
@@ -951,7 +975,7 @@
         <v>18</v>
       </c>
       <c r="C9">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D9">
         <v>0</v>
@@ -960,13 +984,13 @@
         <v>3</v>
       </c>
       <c r="F9">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G9">
-        <v>75</v>
+        <v>76.92</v>
       </c>
       <c r="H9">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
     </row>
   </sheetData>
@@ -1192,7 +1216,7 @@
         <v>18</v>
       </c>
       <c r="C9">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D9">
         <v>0</v>
@@ -1201,13 +1225,13 @@
         <v>3</v>
       </c>
       <c r="F9">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G9">
-        <v>75</v>
+        <v>76.92</v>
       </c>
       <c r="H9">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
     </row>
   </sheetData>
@@ -1217,7 +1241,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1255,10 +1279,10 @@
         <v>25</v>
       </c>
       <c r="C2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D2" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="E2" t="s">
         <v>10</v>
@@ -1272,16 +1296,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920100</v>
+        <v>21330051920386</v>
       </c>
       <c r="B3" t="s">
         <v>26</v>
       </c>
       <c r="C3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D3" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
@@ -1295,16 +1319,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920213</v>
+        <v>20330051920100</v>
       </c>
       <c r="B4" t="s">
         <v>27</v>
       </c>
       <c r="C4" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D4" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="E4" t="s">
         <v>10</v>
@@ -1318,22 +1342,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920235</v>
+        <v>21330051920213</v>
       </c>
       <c r="B5" t="s">
         <v>28</v>
       </c>
       <c r="C5" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D5" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -1341,24 +1365,93 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920082</v>
+        <v>20330051920235</v>
       </c>
       <c r="B6" t="s">
         <v>29</v>
       </c>
       <c r="C6" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D6" t="s">
+        <v>44</v>
+      </c>
+      <c r="E6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>21330051920311</v>
+      </c>
+      <c r="B7" t="s">
+        <v>30</v>
+      </c>
+      <c r="C7" t="s">
+        <v>37</v>
+      </c>
+      <c r="D7" t="s">
+        <v>45</v>
+      </c>
+      <c r="E7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F7" t="s">
+        <v>16</v>
+      </c>
+      <c r="G7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>21330051920328</v>
+      </c>
+      <c r="B8" t="s">
+        <v>31</v>
+      </c>
+      <c r="C8" t="s">
+        <v>38</v>
+      </c>
+      <c r="D8" t="s">
+        <v>46</v>
+      </c>
+      <c r="E8" t="s">
+        <v>10</v>
+      </c>
+      <c r="F8" t="s">
+        <v>16</v>
+      </c>
+      <c r="G8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>21330051920082</v>
+      </c>
+      <c r="B9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C9" t="s">
         <v>39</v>
       </c>
-      <c r="E6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F6" t="s">
+      <c r="D9" t="s">
+        <v>47</v>
+      </c>
+      <c r="E9" t="s">
+        <v>10</v>
+      </c>
+      <c r="F9" t="s">
         <v>17</v>
       </c>
-      <c r="G6">
+      <c r="G9">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Jiménez Nieto Enrique - Estadisticos 20231.xlsx
+++ b/docentes/Jiménez Nieto Enrique - Estadisticos 20231.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="34">
   <si>
     <t>Mat</t>
   </si>
@@ -94,73 +94,31 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>TENTZOHUA</t>
-  </si>
-  <si>
-    <t>LORENZO</t>
-  </si>
-  <si>
-    <t>NUBE</t>
-  </si>
-  <si>
-    <t>VENTURA</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>OFICIAL</t>
-  </si>
-  <si>
-    <t>TRUJILLO</t>
-  </si>
-  <si>
     <t>DE JESUS</t>
   </si>
   <si>
-    <t>LEON</t>
-  </si>
-  <si>
-    <t>ALEMAN</t>
-  </si>
-  <si>
-    <t>ROSALES</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>VILLASEÑOR</t>
-  </si>
-  <si>
-    <t>OSORIO</t>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
   </si>
   <si>
     <t>BRETON</t>
   </si>
   <si>
-    <t>RUBI</t>
-  </si>
-  <si>
-    <t>GREGORIO</t>
-  </si>
-  <si>
-    <t>CHRISTIAN YAIR</t>
-  </si>
-  <si>
-    <t>GUSTAVO</t>
-  </si>
-  <si>
-    <t>JOSE RAFAEL</t>
-  </si>
-  <si>
-    <t>MONICA AIME</t>
-  </si>
-  <si>
-    <t>KARINA YOSELIN</t>
+    <t>VERA</t>
+  </si>
+  <si>
+    <t>CAMPOS</t>
   </si>
   <si>
     <t>VANESSA AMAIRANY</t>
+  </si>
+  <si>
+    <t>MARIA JOSE</t>
+  </si>
+  <si>
+    <t>MARIA TERESA</t>
   </si>
 </sst>
 </file>
@@ -1046,16 +1004,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F2">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="G2">
-        <v>96.3</v>
+        <v>88.89</v>
       </c>
       <c r="H2">
-        <v>8.300000000000001</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1072,13 +1030,13 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F3">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="G3">
-        <v>75</v>
+        <v>87.5</v>
       </c>
       <c r="H3">
         <v>7.6</v>
@@ -1118,16 +1076,16 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F5">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G5">
-        <v>96.67</v>
+        <v>100</v>
       </c>
       <c r="H5">
-        <v>8.300000000000001</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1144,16 +1102,16 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F6">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="G6">
-        <v>77.78</v>
+        <v>96.3</v>
       </c>
       <c r="H6">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1170,16 +1128,16 @@
         <v>0</v>
       </c>
       <c r="E7">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F7">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="G7">
-        <v>91.67</v>
+        <v>100</v>
       </c>
       <c r="H7">
-        <v>8.800000000000001</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1196,16 +1154,16 @@
         <v>0</v>
       </c>
       <c r="E8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F8">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G8">
-        <v>84.84999999999999</v>
+        <v>87.88</v>
       </c>
       <c r="H8">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -1222,13 +1180,13 @@
         <v>0</v>
       </c>
       <c r="E9">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F9">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G9">
-        <v>76.92</v>
+        <v>92.31</v>
       </c>
       <c r="H9">
         <v>7.8</v>
@@ -1241,7 +1199,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1273,16 +1231,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920107</v>
+        <v>21330051920082</v>
       </c>
       <c r="B2" t="s">
         <v>25</v>
       </c>
       <c r="C2" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D2" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="E2" t="s">
         <v>10</v>
@@ -1296,7 +1254,7 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920386</v>
+        <v>21330051920109</v>
       </c>
       <c r="B3" t="s">
         <v>26</v>
@@ -1305,13 +1263,13 @@
         <v>29</v>
       </c>
       <c r="D3" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -1319,139 +1277,24 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920100</v>
+        <v>21330051920260</v>
       </c>
       <c r="B4" t="s">
         <v>27</v>
       </c>
       <c r="C4" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="D4" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="E4" t="s">
         <v>10</v>
       </c>
       <c r="F4" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>21330051920213</v>
-      </c>
-      <c r="B5" t="s">
-        <v>28</v>
-      </c>
-      <c r="C5" t="s">
-        <v>35</v>
-      </c>
-      <c r="D5" t="s">
-        <v>43</v>
-      </c>
-      <c r="E5" t="s">
-        <v>10</v>
-      </c>
-      <c r="F5" t="s">
-        <v>15</v>
-      </c>
-      <c r="G5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>20330051920235</v>
-      </c>
-      <c r="B6" t="s">
-        <v>29</v>
-      </c>
-      <c r="C6" t="s">
-        <v>36</v>
-      </c>
-      <c r="D6" t="s">
-        <v>44</v>
-      </c>
-      <c r="E6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F6" t="s">
-        <v>16</v>
-      </c>
-      <c r="G6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>21330051920311</v>
-      </c>
-      <c r="B7" t="s">
-        <v>30</v>
-      </c>
-      <c r="C7" t="s">
-        <v>37</v>
-      </c>
-      <c r="D7" t="s">
-        <v>45</v>
-      </c>
-      <c r="E7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F7" t="s">
-        <v>16</v>
-      </c>
-      <c r="G7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>21330051920328</v>
-      </c>
-      <c r="B8" t="s">
-        <v>31</v>
-      </c>
-      <c r="C8" t="s">
-        <v>38</v>
-      </c>
-      <c r="D8" t="s">
-        <v>46</v>
-      </c>
-      <c r="E8" t="s">
-        <v>10</v>
-      </c>
-      <c r="F8" t="s">
-        <v>16</v>
-      </c>
-      <c r="G8">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>21330051920082</v>
-      </c>
-      <c r="B9" t="s">
-        <v>32</v>
-      </c>
-      <c r="C9" t="s">
-        <v>39</v>
-      </c>
-      <c r="D9" t="s">
-        <v>47</v>
-      </c>
-      <c r="E9" t="s">
-        <v>10</v>
-      </c>
-      <c r="F9" t="s">
-        <v>17</v>
-      </c>
-      <c r="G9">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Jiménez Nieto Enrique - Estadisticos 20231.xlsx
+++ b/docentes/Jiménez Nieto Enrique - Estadisticos 20231.xlsx
@@ -94,31 +94,31 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>DE JESUS</t>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
   </si>
   <si>
     <t>VAZQUEZ</t>
   </si>
   <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>BRETON</t>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>CAMPOS</t>
   </si>
   <si>
     <t>VERA</t>
   </si>
   <si>
-    <t>CAMPOS</t>
-  </si>
-  <si>
-    <t>VANESSA AMAIRANY</t>
+    <t>MIROSLAVA</t>
+  </si>
+  <si>
+    <t>MARIA TERESA</t>
   </si>
   <si>
     <t>MARIA JOSE</t>
-  </si>
-  <si>
-    <t>MARIA TERESA</t>
   </si>
 </sst>
 </file>
@@ -1231,7 +1231,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920082</v>
+        <v>21330051920078</v>
       </c>
       <c r="B2" t="s">
         <v>25</v>
@@ -1254,7 +1254,7 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920109</v>
+        <v>21330051920260</v>
       </c>
       <c r="B3" t="s">
         <v>26</v>
@@ -1272,12 +1272,12 @@
         <v>17</v>
       </c>
       <c r="G3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920260</v>
+        <v>21330051920109</v>
       </c>
       <c r="B4" t="s">
         <v>27</v>

--- a/docentes/Jiménez Nieto Enrique - Estadisticos 20231.xlsx
+++ b/docentes/Jiménez Nieto Enrique - Estadisticos 20231.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="31">
   <si>
     <t>Mat</t>
   </si>
@@ -94,25 +94,16 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
     <t>VAZQUEZ</t>
   </si>
   <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
     <t>CAMPOS</t>
   </si>
   <si>
     <t>VERA</t>
-  </si>
-  <si>
-    <t>MIROSLAVA</t>
   </si>
   <si>
     <t>MARIA TERESA</t>
@@ -1199,7 +1190,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1231,16 +1222,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920078</v>
+        <v>21330051920260</v>
       </c>
       <c r="B2" t="s">
         <v>25</v>
       </c>
       <c r="C2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E2" t="s">
         <v>10</v>
@@ -1254,16 +1245,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920260</v>
+        <v>21330051920109</v>
       </c>
       <c r="B3" t="s">
         <v>26</v>
       </c>
       <c r="C3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
@@ -1272,30 +1263,7 @@
         <v>17</v>
       </c>
       <c r="G3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>21330051920109</v>
-      </c>
-      <c r="B4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C4" t="s">
-        <v>30</v>
-      </c>
-      <c r="D4" t="s">
-        <v>33</v>
-      </c>
-      <c r="E4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F4" t="s">
-        <v>17</v>
-      </c>
-      <c r="G4">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Jiménez Nieto Enrique - Estadisticos 20231.xlsx
+++ b/docentes/Jiménez Nieto Enrique - Estadisticos 20231.xlsx
@@ -559,7 +559,7 @@
         <v>13</v>
       </c>
       <c r="C4">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="D4">
         <v>0</v>
@@ -568,7 +568,13 @@
         <v>0</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>19</v>
+      </c>
+      <c r="G4">
+        <v>100</v>
+      </c>
+      <c r="H4">
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -800,7 +806,7 @@
         <v>13</v>
       </c>
       <c r="C4">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="D4">
         <v>0</v>
@@ -809,7 +815,13 @@
         <v>0</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>19</v>
+      </c>
+      <c r="G4">
+        <v>100</v>
+      </c>
+      <c r="H4">
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1041,7 +1053,7 @@
         <v>13</v>
       </c>
       <c r="C4">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="D4">
         <v>0</v>
@@ -1050,7 +1062,13 @@
         <v>0</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>19</v>
+      </c>
+      <c r="G4">
+        <v>100</v>
+      </c>
+      <c r="H4">
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:8">

--- a/docentes/Jiménez Nieto Enrique - Estadisticos 20231.xlsx
+++ b/docentes/Jiménez Nieto Enrique - Estadisticos 20231.xlsx
@@ -1016,7 +1016,7 @@
         <v>88.89</v>
       </c>
       <c r="H2">
-        <v>7.9</v>
+        <v>9.4</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1042,7 +1042,7 @@
         <v>87.5</v>
       </c>
       <c r="H3">
-        <v>7.6</v>
+        <v>9.4</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1094,7 +1094,7 @@
         <v>100</v>
       </c>
       <c r="H5">
-        <v>8.1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1120,7 +1120,7 @@
         <v>96.3</v>
       </c>
       <c r="H6">
-        <v>8.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1146,7 +1146,7 @@
         <v>100</v>
       </c>
       <c r="H7">
-        <v>8.9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1172,7 +1172,7 @@
         <v>87.88</v>
       </c>
       <c r="H8">
-        <v>8.1</v>
+        <v>9.4</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -1198,7 +1198,7 @@
         <v>92.31</v>
       </c>
       <c r="H9">
-        <v>7.8</v>
+        <v>9.6</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Jiménez Nieto Enrique - Estadisticos 20231.xlsx
+++ b/docentes/Jiménez Nieto Enrique - Estadisticos 20231.xlsx
@@ -1016,7 +1016,7 @@
         <v>88.89</v>
       </c>
       <c r="H2">
-        <v>9.4</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1042,7 +1042,7 @@
         <v>87.5</v>
       </c>
       <c r="H3">
-        <v>9.4</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1094,7 +1094,7 @@
         <v>100</v>
       </c>
       <c r="H5">
-        <v>10</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1120,7 +1120,7 @@
         <v>96.3</v>
       </c>
       <c r="H6">
-        <v>9.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1146,7 +1146,7 @@
         <v>100</v>
       </c>
       <c r="H7">
-        <v>10</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1172,7 +1172,7 @@
         <v>87.88</v>
       </c>
       <c r="H8">
-        <v>9.4</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -1198,7 +1198,7 @@
         <v>92.31</v>
       </c>
       <c r="H9">
-        <v>9.6</v>
+        <v>7.8</v>
       </c>
     </row>
   </sheetData>
